--- a/uploads/phase1a_data.xlsx
+++ b/uploads/phase1a_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fdae77fc648ca8d/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fdae77fc648ca8d/Desktop/SAAS_MENU/saas-menu-app-backend/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E3D70CA5-E670-4E7F-A91C-2BB673E32AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554B0A01-5792-41B6-93B8-5D7E9E9008EE}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="8_{E3D70CA5-E670-4E7F-A91C-2BB673E32AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78F5D4CD-F0CE-42DF-940F-3758D14840C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F031C08-4A49-45EA-A80F-0B2E02A2906C}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,17 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="94">
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>serviceId</t>
-  </si>
-  <si>
-    <t>categoryId</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -68,21 +60,12 @@
     <t>Restaurant</t>
   </si>
   <si>
-    <t>Main dining area</t>
-  </si>
-  <si>
     <t>Bar</t>
   </si>
   <si>
-    <t>Bar service with alcoholic drinks</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
-    <t>643fServiceID1</t>
-  </si>
-  <si>
     <t>North Indian</t>
   </si>
   <si>
@@ -92,42 +75,18 @@
     <t>South Indian</t>
   </si>
   <si>
-    <t>Dosa, Idli, Sambar</t>
-  </si>
-  <si>
-    <t>Chinese</t>
-  </si>
-  <si>
-    <t>Indo-Chinese specialties</t>
-  </si>
-  <si>
-    <t>643fServiceID2</t>
-  </si>
-  <si>
     <t>Cocktails</t>
   </si>
   <si>
-    <t>Mixed alcoholic drinks</t>
-  </si>
-  <si>
     <t>Mocktails</t>
   </si>
   <si>
-    <t>Non-alcoholic mixed drinks</t>
-  </si>
-  <si>
     <t>item</t>
   </si>
   <si>
-    <t>643fCategoryID1</t>
-  </si>
-  <si>
     <t>Paneer Butter Masala</t>
   </si>
   <si>
-    <t>Rich tomato gravy with paneer</t>
-  </si>
-  <si>
     <t>veg</t>
   </si>
   <si>
@@ -146,61 +105,217 @@
     <t>Serves 2</t>
   </si>
   <si>
-    <t>643fCategoryID2</t>
-  </si>
-  <si>
     <t>Masala Dosa</t>
   </si>
   <si>
-    <t>Crisp dosa with masala filling</t>
-  </si>
-  <si>
     <t>Single</t>
   </si>
   <si>
     <t>Idli-Vada Combo</t>
   </si>
   <si>
-    <t>2 Idlis + 1 Vada + Sambar</t>
-  </si>
-  <si>
-    <t>643fCategoryID3</t>
-  </si>
-  <si>
-    <t>Veg Manchurian</t>
-  </si>
-  <si>
-    <t>Indo-Chinese gravy with veggies</t>
-  </si>
-  <si>
-    <t>Chicken Hakka Noodles</t>
-  </si>
-  <si>
-    <t>Classic Indo-Chinese noodles</t>
-  </si>
-  <si>
-    <t>643fCategoryID4</t>
-  </si>
-  <si>
-    <t>Mojito</t>
-  </si>
-  <si>
-    <t>Refreshing mint + lime cocktail</t>
-  </si>
-  <si>
     <t>Glass</t>
   </si>
   <si>
-    <t>643fCategoryID5</t>
-  </si>
-  <si>
     <t>Virgin Pina Colada</t>
   </si>
   <si>
-    <t>Coconut + pineapple mocktail</t>
-  </si>
-  <si>
     <t>67cd67486f1f071d76054ca0</t>
+  </si>
+  <si>
+    <t>restaurantId</t>
+  </si>
+  <si>
+    <t>serviceName</t>
+  </si>
+  <si>
+    <t>categoryName</t>
+  </si>
+  <si>
+    <t>Primary dining service</t>
+  </si>
+  <si>
+    <t>Cocktails and drinks</t>
+  </si>
+  <si>
+    <t>Cafe</t>
+  </si>
+  <si>
+    <t>Hot beverages &amp; light snacks</t>
+  </si>
+  <si>
+    <t>Sweet Station</t>
+  </si>
+  <si>
+    <t>Indian sweets &amp; desserts</t>
+  </si>
+  <si>
+    <t>Famous South Indian delicacies</t>
+  </si>
+  <si>
+    <t>Alcoholic mixed drinks</t>
+  </si>
+  <si>
+    <t>Refreshing non-alcoholic drinks</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>Chai, coffee, juices</t>
+  </si>
+  <si>
+    <t>Snacks</t>
+  </si>
+  <si>
+    <t>Light eats &amp; sandwiches</t>
+  </si>
+  <si>
+    <t>Mithai</t>
+  </si>
+  <si>
+    <t>Traditional Indian sweets</t>
+  </si>
+  <si>
+    <t>Dessert</t>
+  </si>
+  <si>
+    <t>Western-style desserts</t>
+  </si>
+  <si>
+    <t>Paneer in rich tomato gravy</t>
+  </si>
+  <si>
+    <t>Crispy dosa with spiced potato</t>
+  </si>
+  <si>
+    <t>Steamed rice cakes + deep-fried vada</t>
+  </si>
+  <si>
+    <t>Filter Coffee</t>
+  </si>
+  <si>
+    <t>Cup</t>
+  </si>
+  <si>
+    <t>Strong South Indian coffee</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>Long Island Iced Tea</t>
+  </si>
+  <si>
+    <t>Mixed spirits with cola</t>
+  </si>
+  <si>
+    <t>Bloody Mary</t>
+  </si>
+  <si>
+    <t>Tomato juice &amp; vodka</t>
+  </si>
+  <si>
+    <t>Virgin Mojito</t>
+  </si>
+  <si>
+    <t>Mint-lime non-alcoholic</t>
+  </si>
+  <si>
+    <t>Shirley Temple</t>
+  </si>
+  <si>
+    <t>Ginger ale + grenadine</t>
+  </si>
+  <si>
+    <t>Pineapple + coconut mocktail</t>
+  </si>
+  <si>
+    <t>Masala Chai</t>
+  </si>
+  <si>
+    <t>Spiced Indian tea</t>
+  </si>
+  <si>
+    <t>Cappuccino</t>
+  </si>
+  <si>
+    <t>Espresso + steamed milk</t>
+  </si>
+  <si>
+    <t>Fresh Juice</t>
+  </si>
+  <si>
+    <t>Seasonal fruit juice</t>
+  </si>
+  <si>
+    <t>Grilled Sandwich</t>
+  </si>
+  <si>
+    <t>Cheese &amp; veggie sandwich</t>
+  </si>
+  <si>
+    <t>Samosa</t>
+  </si>
+  <si>
+    <t>Deep-fried potato pastry</t>
+  </si>
+  <si>
+    <t>Paneer Kathi Roll</t>
+  </si>
+  <si>
+    <t>Wrap with paneer &amp; veggies</t>
+  </si>
+  <si>
+    <t>Gulab Jamun</t>
+  </si>
+  <si>
+    <t>Deep-fried milk balls in syrup</t>
+  </si>
+  <si>
+    <t>Jalebi</t>
+  </si>
+  <si>
+    <t>Crispy sugar syrup spirals</t>
+  </si>
+  <si>
+    <t>Rasgulla</t>
+  </si>
+  <si>
+    <t>Spongy cottage cheese balls</t>
+  </si>
+  <si>
+    <t>Brownie Sundae</t>
+  </si>
+  <si>
+    <t>Warm brownie with ice cream</t>
+  </si>
+  <si>
+    <t>Cheesecake</t>
+  </si>
+  <si>
+    <t>Slice</t>
+  </si>
+  <si>
+    <t>Rich creamy dessert</t>
+  </si>
+  <si>
+    <t>Fruit Custard</t>
+  </si>
+  <si>
+    <t>Mixed fruits in sweet custard</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>Mushroom Masala</t>
+  </si>
+  <si>
+    <t>Smoky mushroom</t>
+  </si>
+  <si>
+    <t>lime cocktail</t>
   </si>
 </sst>
 </file>
@@ -281,10 +396,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -322,7 +441,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -428,7 +547,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -570,7 +689,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -578,312 +697,828 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB837DDE-46D0-4213-899F-2B025E157846}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9">
-        <v>220</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
-        <v>280</v>
-      </c>
-      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
       <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11">
-        <v>90</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14">
+        <v>220</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15">
+        <v>380</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16">
+        <v>250</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19">
+        <v>50</v>
+      </c>
+      <c r="G19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20">
+        <v>250</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21">
+        <v>350</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22">
+        <v>300</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24">
+        <v>130</v>
+      </c>
+      <c r="G24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25">
+        <v>180</v>
+      </c>
+      <c r="G25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26">
         <v>40</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
         <v>41</v>
       </c>
-      <c r="F12">
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27">
+        <v>120</v>
+      </c>
+      <c r="G27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28">
+        <v>90</v>
+      </c>
+      <c r="G28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" t="s">
         <v>70</v>
       </c>
-      <c r="G12" t="s">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30">
         <v>30</v>
       </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G30" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
         <v>43</v>
       </c>
-      <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13">
+      <c r="E31" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32">
+        <v>60</v>
+      </c>
+      <c r="G32" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33">
+        <v>50</v>
+      </c>
+      <c r="G33" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34">
+        <v>60</v>
+      </c>
+      <c r="G34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35">
+        <v>120</v>
+      </c>
+      <c r="G35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36">
         <v>150</v>
       </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14">
-        <v>180</v>
-      </c>
-      <c r="G14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="G36" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" t="s">
+        <v>86</v>
+      </c>
+      <c r="I36" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" t="s">
         <v>47</v>
       </c>
-      <c r="D15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>250</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="E37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" t="s">
         <v>53</v>
       </c>
-      <c r="F16">
-        <v>180</v>
-      </c>
-      <c r="G16" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" t="s">
-        <v>50</v>
+      <c r="I37" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
